--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.99</v>
+        <v>0.9983333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7783333333333333</v>
+        <v>0.7483333333333333</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9925</v>
+        <v>0.998</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9983333333333333</v>
+        <v>0.9933333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7483333333333333</v>
+        <v>0.8133333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.998</v>
+        <v>0.9893333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,27 +445,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9933333333333333</v>
+        <v>0.9916666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Validation Accuracy</t>
+          <t>External Validation Accuracy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8133333333333334</v>
+        <v>0.8166666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cross Validation</t>
+          <t>Cross Validation Mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9893333333333333</v>
+        <v>0.9886666666666667</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Cross Validation Std</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.00710242525088749</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>0.8393075980392157</v>
       </c>
     </row>
     <row r="3">
@@ -445,7 +445,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9916666666666667</v>
+        <v>0.7795468462951622</v>
       </c>
     </row>
     <row r="4">
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8166666666666667</v>
+        <v>0.6094771241830066</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9886666666666667</v>
+        <v>0.735323160188754</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00710242525088749</v>
+        <v>0.0549939143815346</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,7 +435,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8393075980392157</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -445,37 +445,27 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7795468462951622</v>
+        <v>0.9933333333333333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>External Validation Accuracy</t>
+          <t>Validation Accuracy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6094771241830066</v>
+        <v>0.8133333333333334</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cross Validation Mean</t>
+          <t>Cross Validation</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.735323160188754</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Cross Validation Std</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.0549939143815346</v>
+        <v>0.9893333333333333</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,27 +445,17 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9933333333333333</v>
+        <v>0.94375</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Validation Accuracy</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.8133333333333334</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
           <t>Cross Validation</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0.9893333333333333</v>
+      <c r="B4" t="n">
+        <v>0.9198427672955976</v>
       </c>
     </row>
   </sheetData>

--- a/training_metrics.xlsx
+++ b/training_metrics.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,17 +445,107 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.94375</v>
+        <v>0.9125</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cross Validation</t>
+          <t>Train-Test Gap</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9198427672955976</v>
+        <v>0.08750000000000002</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cross Validation Accuracy</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9185927672955975</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9225430597771023</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.9125</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F1-Score</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.9136160677291365</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Specificity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.956327514253806</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MSE</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.2958039891549808</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.8691512354693616</v>
       </c>
     </row>
   </sheetData>
